--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/50.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/50.xlsx
@@ -426,13 +426,13 @@
         <v>-9.814450359910357</v>
       </c>
       <c r="E2">
-        <v>-17.4331054389719</v>
+        <v>-31.26340016547374</v>
       </c>
       <c r="F2">
-        <v>-5.27555569932969</v>
+        <v>-5.785327200440686</v>
       </c>
       <c r="G2">
-        <v>-11.60698237572209</v>
+        <v>-19.4398539565499</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.755317449010926</v>
       </c>
       <c r="E3">
-        <v>-18.56220344872638</v>
+        <v>-31.48689394317429</v>
       </c>
       <c r="F3">
-        <v>-5.011275848242744</v>
+        <v>-5.73755856579085</v>
       </c>
       <c r="G3">
-        <v>-12.41564933459986</v>
+        <v>-20.05078037509424</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.635352534330368</v>
       </c>
       <c r="E4">
-        <v>-18.16461701627494</v>
+        <v>-30.85225321760634</v>
       </c>
       <c r="F4">
-        <v>-5.152408944494709</v>
+        <v>-5.799847652644358</v>
       </c>
       <c r="G4">
-        <v>-12.12349038021364</v>
+        <v>-20.00777969908464</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.454785398852506</v>
       </c>
       <c r="E5">
-        <v>-18.80073176013239</v>
+        <v>-32.51386127863378</v>
       </c>
       <c r="F5">
-        <v>-4.997239162602306</v>
+        <v>-5.770867219057418</v>
       </c>
       <c r="G5">
-        <v>-12.41278240216285</v>
+        <v>-19.81935503389872</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.214697086051578</v>
       </c>
       <c r="E6">
-        <v>-19.7375009503071</v>
+        <v>-32.00812582993116</v>
       </c>
       <c r="F6">
-        <v>-5.098893925171653</v>
+        <v>-5.737456676600305</v>
       </c>
       <c r="G6">
-        <v>-11.37655185346112</v>
+        <v>-19.68984980294796</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.917333580387426</v>
       </c>
       <c r="E7">
-        <v>-20.10394053853378</v>
+        <v>-32.79667127312381</v>
       </c>
       <c r="F7">
-        <v>-5.184134587654528</v>
+        <v>-5.641023942138206</v>
       </c>
       <c r="G7">
-        <v>-11.79092290697507</v>
+        <v>-19.91694329530535</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.565983681185498</v>
       </c>
       <c r="E8">
-        <v>-19.34343314215963</v>
+        <v>-33.17082738105955</v>
       </c>
       <c r="F8">
-        <v>-4.743825835105284</v>
+        <v>-5.506468911431871</v>
       </c>
       <c r="G8">
-        <v>-11.61438144500236</v>
+        <v>-18.90308872390355</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.166875541883954</v>
       </c>
       <c r="E9">
-        <v>-19.86774891971572</v>
+        <v>-33.92913620330298</v>
       </c>
       <c r="F9">
-        <v>-4.810381842450613</v>
+        <v>-5.54880842612376</v>
       </c>
       <c r="G9">
-        <v>-11.5366266619215</v>
+        <v>-18.9946087553367</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.727281141364714</v>
       </c>
       <c r="E10">
-        <v>-20.64690457205345</v>
+        <v>-34.44671134729865</v>
       </c>
       <c r="F10">
-        <v>-4.73707215567026</v>
+        <v>-5.452523141059359</v>
       </c>
       <c r="G10">
-        <v>-12.19979845489384</v>
+        <v>-19.34627476579132</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.259301812058457</v>
       </c>
       <c r="E11">
-        <v>-20.60598528092014</v>
+        <v>-33.70560393357336</v>
       </c>
       <c r="F11">
-        <v>-4.3436879313874</v>
+        <v>-5.480249426398461</v>
       </c>
       <c r="G11">
-        <v>-11.47246497882488</v>
+        <v>-18.83194344499184</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.775586418575782</v>
       </c>
       <c r="E12">
-        <v>-21.28964900185814</v>
+        <v>-34.7403987363551</v>
       </c>
       <c r="F12">
-        <v>-4.101974465087518</v>
+        <v>-5.414523443190737</v>
       </c>
       <c r="G12">
-        <v>-11.35221934374747</v>
+        <v>-18.91115486810999</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.287181506800432</v>
       </c>
       <c r="E13">
-        <v>-21.02981874872004</v>
+        <v>-34.86015196725094</v>
       </c>
       <c r="F13">
-        <v>-4.430917504004396</v>
+        <v>-5.387289208088898</v>
       </c>
       <c r="G13">
-        <v>-10.91237033176329</v>
+        <v>-18.96577224841688</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.812763286031573</v>
       </c>
       <c r="E14">
-        <v>-23.23014539888496</v>
+        <v>-34.70214671641231</v>
       </c>
       <c r="F14">
-        <v>-3.837846205235285</v>
+        <v>-5.126029584552559</v>
       </c>
       <c r="G14">
-        <v>-11.14252938929004</v>
+        <v>-18.05638359677955</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.366959720641322</v>
       </c>
       <c r="E15">
-        <v>-23.55810654346847</v>
+        <v>-36.07005606719829</v>
       </c>
       <c r="F15">
-        <v>-4.051561681687946</v>
+        <v>-5.051580064225954</v>
       </c>
       <c r="G15">
-        <v>-10.90409396791511</v>
+        <v>-17.93306246489616</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.963624537545633</v>
       </c>
       <c r="E16">
-        <v>-23.74904965000189</v>
+        <v>-36.1792307828122</v>
       </c>
       <c r="F16">
-        <v>-3.694141856565029</v>
+        <v>-4.903802633036134</v>
       </c>
       <c r="G16">
-        <v>-9.964832608604167</v>
+        <v>-17.97361995829777</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.615416660591055</v>
       </c>
       <c r="E17">
-        <v>-22.83527152236412</v>
+        <v>-36.32244150906777</v>
       </c>
       <c r="F17">
-        <v>-3.287086256666366</v>
+        <v>-4.784401755596613</v>
       </c>
       <c r="G17">
-        <v>-9.924692243940504</v>
+        <v>-17.685819337114</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.331508812676308</v>
       </c>
       <c r="E18">
-        <v>-25.00119988396679</v>
+        <v>-36.98276321073323</v>
       </c>
       <c r="F18">
-        <v>-3.270664701273268</v>
+        <v>-4.689899945550439</v>
       </c>
       <c r="G18">
-        <v>-9.593243735094212</v>
+        <v>-17.09807997952672</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.120876754038639</v>
       </c>
       <c r="E19">
-        <v>-23.99586506884194</v>
+        <v>-37.54369396487834</v>
       </c>
       <c r="F19">
-        <v>-3.115239782220803</v>
+        <v>-4.553559783091071</v>
       </c>
       <c r="G19">
-        <v>-9.584202635226463</v>
+        <v>-17.07954920087065</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.989598602774624</v>
       </c>
       <c r="E20">
-        <v>-25.65480812291587</v>
+        <v>-38.27572405245526</v>
       </c>
       <c r="F20">
-        <v>-2.808962532179325</v>
+        <v>-4.436214913545299</v>
       </c>
       <c r="G20">
-        <v>-9.276659575719247</v>
+        <v>-16.98821621526047</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.938787786128444</v>
       </c>
       <c r="E21">
-        <v>-26.37608082048757</v>
+        <v>-38.79520341977116</v>
       </c>
       <c r="F21">
-        <v>-2.545565720743763</v>
+        <v>-4.428390155058455</v>
       </c>
       <c r="G21">
-        <v>-10.12383811085536</v>
+        <v>-16.84379366610976</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.968642776553767</v>
       </c>
       <c r="E22">
-        <v>-26.04025824502675</v>
+        <v>-39.01830095599604</v>
       </c>
       <c r="F22">
-        <v>-2.880073731872649</v>
+        <v>-4.088161438645836</v>
       </c>
       <c r="G22">
-        <v>-9.774337197183424</v>
+        <v>-17.03299299895188</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.076315050142863</v>
       </c>
       <c r="E23">
-        <v>-26.26281462860772</v>
+        <v>-39.49712594790807</v>
       </c>
       <c r="F23">
-        <v>-2.344187948388398</v>
+        <v>-4.14676511892429</v>
       </c>
       <c r="G23">
-        <v>-9.537371658027933</v>
+        <v>-16.78740183339382</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.254928359561595</v>
       </c>
       <c r="E24">
-        <v>-26.42367055383417</v>
+        <v>-39.33813575397278</v>
       </c>
       <c r="F24">
-        <v>-2.637174871819361</v>
+        <v>-3.770789863978664</v>
       </c>
       <c r="G24">
-        <v>-9.823058495884879</v>
+        <v>-16.94121640023943</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.494834845262122</v>
       </c>
       <c r="E25">
-        <v>-26.73398876368379</v>
+        <v>-39.77766944115726</v>
       </c>
       <c r="F25">
-        <v>-2.601606432277956</v>
+        <v>-3.764271440886035</v>
       </c>
       <c r="G25">
-        <v>-9.367010984577037</v>
+        <v>-16.90332224072417</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.783292107274809</v>
       </c>
       <c r="E26">
-        <v>-25.29495746437036</v>
+        <v>-39.78323040723868</v>
       </c>
       <c r="F26">
-        <v>-2.348822664007061</v>
+        <v>-3.82531963337015</v>
       </c>
       <c r="G26">
-        <v>-9.144585361430023</v>
+        <v>-16.56324976074807</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.105442650199542</v>
       </c>
       <c r="E27">
-        <v>-26.19393201047705</v>
+        <v>-39.02835643253007</v>
       </c>
       <c r="F27">
-        <v>-2.228228937507509</v>
+        <v>-3.882736263160393</v>
       </c>
       <c r="G27">
-        <v>-9.814295481842429</v>
+        <v>-17.04561279854758</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.448436738718365</v>
       </c>
       <c r="E28">
-        <v>-26.52618614841982</v>
+        <v>-39.92047486898915</v>
       </c>
       <c r="F28">
-        <v>-2.094520498286836</v>
+        <v>-4.061825153808631</v>
       </c>
       <c r="G28">
-        <v>-9.485809911253783</v>
+        <v>-17.52273193221288</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.797708724303486</v>
       </c>
       <c r="E29">
-        <v>-26.17447315766609</v>
+        <v>-39.76061520804438</v>
       </c>
       <c r="F29">
-        <v>-2.514501943138782</v>
+        <v>-4.099092574893178</v>
       </c>
       <c r="G29">
-        <v>-9.888776135384951</v>
+        <v>-16.58183350813277</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.138841386303937</v>
       </c>
       <c r="E30">
-        <v>-26.29370334981404</v>
+        <v>-39.60038194799397</v>
       </c>
       <c r="F30">
-        <v>-2.577595374740409</v>
+        <v>-3.892436445447175</v>
       </c>
       <c r="G30">
-        <v>-10.04964216422922</v>
+        <v>-16.96154149457779</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.460611616626328</v>
       </c>
       <c r="E31">
-        <v>-25.06586196432231</v>
+        <v>-40.23094931119203</v>
       </c>
       <c r="F31">
-        <v>-2.495220863471221</v>
+        <v>-3.817904916747692</v>
       </c>
       <c r="G31">
-        <v>-9.936229495144865</v>
+        <v>-17.31209185118568</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.751875973928906</v>
       </c>
       <c r="E32">
-        <v>-25.91522254920096</v>
+        <v>-39.56880263450148</v>
       </c>
       <c r="F32">
-        <v>-2.462528515552335</v>
+        <v>-4.005985735553319</v>
       </c>
       <c r="G32">
-        <v>-10.34352260229586</v>
+        <v>-17.41392257670089</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.003568467319783</v>
       </c>
       <c r="E33">
-        <v>-25.29227660775781</v>
+        <v>-38.67181382424716</v>
       </c>
       <c r="F33">
-        <v>-2.415132646233759</v>
+        <v>-3.879350725585151</v>
       </c>
       <c r="G33">
-        <v>-10.51577359724968</v>
+        <v>-17.08689861196783</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.209119031363581</v>
       </c>
       <c r="E34">
-        <v>-24.51694751595656</v>
+        <v>-37.78507295067219</v>
       </c>
       <c r="F34">
-        <v>-2.518657034031224</v>
+        <v>-3.841922601224461</v>
       </c>
       <c r="G34">
-        <v>-10.356979969913</v>
+        <v>-17.67870663002288</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.362291551536661</v>
       </c>
       <c r="E35">
-        <v>-24.0227642044475</v>
+        <v>-38.63987223283405</v>
       </c>
       <c r="F35">
-        <v>-2.651402910329845</v>
+        <v>-3.817439374267319</v>
       </c>
       <c r="G35">
-        <v>-10.15469570582691</v>
+        <v>-17.59937602726532</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.464658157562766</v>
       </c>
       <c r="E36">
-        <v>-24.1088414383853</v>
+        <v>-38.42586107970556</v>
       </c>
       <c r="F36">
-        <v>-2.565378612283922</v>
+        <v>-4.134560781978845</v>
       </c>
       <c r="G36">
-        <v>-9.913750890933214</v>
+        <v>-17.51938166012714</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.519686383773794</v>
       </c>
       <c r="E37">
-        <v>-24.72516675082924</v>
+        <v>-37.58610085972317</v>
       </c>
       <c r="F37">
-        <v>-2.512936328747491</v>
+        <v>-3.705140918939401</v>
       </c>
       <c r="G37">
-        <v>-9.726079374857468</v>
+        <v>-17.38048275620871</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.531790096544663</v>
       </c>
       <c r="E38">
-        <v>-23.25476218359066</v>
+        <v>-37.36645628492914</v>
       </c>
       <c r="F38">
-        <v>-2.360508442958354</v>
+        <v>-4.121785699892871</v>
       </c>
       <c r="G38">
-        <v>-10.12516232907107</v>
+        <v>-17.78298053814607</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.509835301379835</v>
       </c>
       <c r="E39">
-        <v>-23.39230099615162</v>
+        <v>-37.65089879429893</v>
       </c>
       <c r="F39">
-        <v>-2.638783561315597</v>
+        <v>-4.034561097480291</v>
       </c>
       <c r="G39">
-        <v>-10.02042328929961</v>
+        <v>-17.42558728390851</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.463448964409984</v>
       </c>
       <c r="E40">
-        <v>-23.47137268079955</v>
+        <v>-36.25366983855029</v>
       </c>
       <c r="F40">
-        <v>-2.558706941221775</v>
+        <v>-3.988999233591513</v>
       </c>
       <c r="G40">
-        <v>-10.53825882255241</v>
+        <v>-17.08436438935752</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.402450731920969</v>
       </c>
       <c r="E41">
-        <v>-23.03964155433029</v>
+        <v>-36.68306880090561</v>
       </c>
       <c r="F41">
-        <v>-2.537277904878754</v>
+        <v>-3.705200561392402</v>
       </c>
       <c r="G41">
-        <v>-10.21004802724352</v>
+        <v>-17.65143270059759</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.336973824492602</v>
       </c>
       <c r="E42">
-        <v>-22.27419812128777</v>
+        <v>-36.21692806468906</v>
       </c>
       <c r="F42">
-        <v>-2.645614278919082</v>
+        <v>-3.9834027834182</v>
       </c>
       <c r="G42">
-        <v>-10.52462599602169</v>
+        <v>-17.45734865781228</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.275229343611255</v>
       </c>
       <c r="E43">
-        <v>-21.30104717093544</v>
+        <v>-35.34724368846398</v>
       </c>
       <c r="F43">
-        <v>-2.818149955043774</v>
+        <v>-3.861047947820296</v>
       </c>
       <c r="G43">
-        <v>-9.701458847681909</v>
+        <v>-17.45089971510178</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.22539840446119</v>
       </c>
       <c r="E44">
-        <v>-21.50150460135898</v>
+        <v>-35.34679763377422</v>
       </c>
       <c r="F44">
-        <v>-2.828322306750152</v>
+        <v>-4.062409981195008</v>
       </c>
       <c r="G44">
-        <v>-10.40803520321964</v>
+        <v>-16.79748409983367</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.196201976561607</v>
       </c>
       <c r="E45">
-        <v>-22.09240253224985</v>
+        <v>-35.46432059122129</v>
       </c>
       <c r="F45">
-        <v>-2.669358602152927</v>
+        <v>-4.32670639963001</v>
       </c>
       <c r="G45">
-        <v>-9.501276780013258</v>
+        <v>-17.48407800249635</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.192615080072152</v>
       </c>
       <c r="E46">
-        <v>-21.11258566815823</v>
+        <v>-35.04636961115736</v>
       </c>
       <c r="F46">
-        <v>-2.78203147954691</v>
+        <v>-3.960185301852535</v>
       </c>
       <c r="G46">
-        <v>-9.586311452734979</v>
+        <v>-17.08352351079055</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.21831412271708</v>
       </c>
       <c r="E47">
-        <v>-21.21079468396258</v>
+        <v>-34.40285986924538</v>
       </c>
       <c r="F47">
-        <v>-2.819740420457149</v>
+        <v>-3.998028438282028</v>
       </c>
       <c r="G47">
-        <v>-9.688014722246928</v>
+        <v>-17.41725464078617</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.276923823530133</v>
       </c>
       <c r="E48">
-        <v>-19.60787338183754</v>
+        <v>-34.81996176043287</v>
       </c>
       <c r="F48">
-        <v>-2.635471748439205</v>
+        <v>-4.388509234818075</v>
       </c>
       <c r="G48">
-        <v>-9.964835919149706</v>
+        <v>-17.09955151701893</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.367895499846858</v>
       </c>
       <c r="E49">
-        <v>-20.10719198287129</v>
+        <v>-34.67774729845898</v>
       </c>
       <c r="F49">
-        <v>-3.072329522388386</v>
+        <v>-4.155197899084789</v>
       </c>
       <c r="G49">
-        <v>-10.02705100146923</v>
+        <v>-17.32706213811426</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.488779239821597</v>
       </c>
       <c r="E50">
-        <v>-20.25545422188241</v>
+        <v>-33.99924377365273</v>
       </c>
       <c r="F50">
-        <v>-3.267727310462941</v>
+        <v>-4.153643881837137</v>
       </c>
       <c r="G50">
-        <v>-9.551762599487144</v>
+        <v>-17.36000041095724</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.634933395578846</v>
       </c>
       <c r="E51">
-        <v>-19.83407518699468</v>
+        <v>-33.01925709178582</v>
       </c>
       <c r="F51">
-        <v>-3.352890934777356</v>
+        <v>-3.994284217621374</v>
       </c>
       <c r="G51">
-        <v>-10.44302104847865</v>
+        <v>-17.22844098649937</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.797304963863736</v>
       </c>
       <c r="E52">
-        <v>-20.03496282244894</v>
+        <v>-33.17032698468171</v>
       </c>
       <c r="F52">
-        <v>-3.197696301862869</v>
+        <v>-4.399789113741996</v>
       </c>
       <c r="G52">
-        <v>-9.564461852175789</v>
+        <v>-17.51572185203348</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.971557991323015</v>
       </c>
       <c r="E53">
-        <v>-20.07245405875845</v>
+        <v>-33.19368711785027</v>
       </c>
       <c r="F53">
-        <v>-3.03941517200555</v>
+        <v>-3.977640659764326</v>
       </c>
       <c r="G53">
-        <v>-9.845298740817702</v>
+        <v>-17.26181459608076</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.150422213999805</v>
       </c>
       <c r="E54">
-        <v>-20.23871698195006</v>
+        <v>-32.34452125735395</v>
       </c>
       <c r="F54">
-        <v>-3.419224111291332</v>
+        <v>-4.261581811156718</v>
       </c>
       <c r="G54">
-        <v>-10.39044958531503</v>
+        <v>-16.9996078024611</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.324900495495145</v>
       </c>
       <c r="E55">
-        <v>-18.79044759566098</v>
+        <v>-32.8129013239673</v>
       </c>
       <c r="F55">
-        <v>-3.583985559340751</v>
+        <v>-4.389726934900191</v>
       </c>
       <c r="G55">
-        <v>-10.7012005634498</v>
+        <v>-17.74958706529144</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.490843851604737</v>
       </c>
       <c r="E56">
-        <v>-18.99749395576567</v>
+        <v>-32.43012526575794</v>
       </c>
       <c r="F56">
-        <v>-3.257775304485708</v>
+        <v>-4.162087430773872</v>
       </c>
       <c r="G56">
-        <v>-9.487349314929544</v>
+        <v>-16.94658113928582</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.642831701625646</v>
       </c>
       <c r="E57">
-        <v>-18.90029026119103</v>
+        <v>-32.17497971898078</v>
       </c>
       <c r="F57">
-        <v>-3.15380028482112</v>
+        <v>-4.323780605963322</v>
       </c>
       <c r="G57">
-        <v>-10.16881187200636</v>
+        <v>-17.1125652715338</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.776380125144556</v>
       </c>
       <c r="E58">
-        <v>-19.28392899369884</v>
+        <v>-31.73116888809605</v>
       </c>
       <c r="F58">
-        <v>-3.472965274915353</v>
+        <v>-4.263994017033671</v>
       </c>
       <c r="G58">
-        <v>-9.453052063142696</v>
+        <v>-17.46811786245153</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.888190896526087</v>
       </c>
       <c r="E59">
-        <v>-19.26907107047967</v>
+        <v>-31.87013416996943</v>
       </c>
       <c r="F59">
-        <v>-3.502634910181423</v>
+        <v>-4.433279179469777</v>
       </c>
       <c r="G59">
-        <v>-9.548488469948804</v>
+        <v>-17.2190357266223</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.973994834023346</v>
       </c>
       <c r="E60">
-        <v>-18.78530324918826</v>
+        <v>-32.14178374026755</v>
       </c>
       <c r="F60">
-        <v>-3.85334992954608</v>
+        <v>-4.29824700913943</v>
       </c>
       <c r="G60">
-        <v>-10.19564384360215</v>
+        <v>-17.94528665429992</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.033427258382035</v>
       </c>
       <c r="E61">
-        <v>-18.84139292824727</v>
+        <v>-31.51829438194348</v>
       </c>
       <c r="F61">
-        <v>-3.555111156781368</v>
+        <v>-4.268987415737746</v>
       </c>
       <c r="G61">
-        <v>-10.60052687360056</v>
+        <v>-17.78072109081552</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.06789779515406</v>
       </c>
       <c r="E62">
-        <v>-18.4943804935135</v>
+        <v>-31.74143946714545</v>
       </c>
       <c r="F62">
-        <v>-3.697114867173676</v>
+        <v>-4.424629367049745</v>
       </c>
       <c r="G62">
-        <v>-9.985063352394654</v>
+        <v>-18.08564219825563</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.077597754292363</v>
       </c>
       <c r="E63">
-        <v>-18.48308195086436</v>
+        <v>-31.15520586448248</v>
       </c>
       <c r="F63">
-        <v>-3.78643275401313</v>
+        <v>-4.42254767976651</v>
       </c>
       <c r="G63">
-        <v>-10.33868258471744</v>
+        <v>-17.51481641782849</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.065531478324058</v>
       </c>
       <c r="E64">
-        <v>-19.53957493685385</v>
+        <v>-31.5559712856873</v>
       </c>
       <c r="F64">
-        <v>-3.548668943489797</v>
+        <v>-4.500942714032649</v>
       </c>
       <c r="G64">
-        <v>-9.8752922834035</v>
+        <v>-17.62798741708847</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.036399731705574</v>
       </c>
       <c r="E65">
-        <v>-19.38480075221969</v>
+        <v>-31.31891925680778</v>
       </c>
       <c r="F65">
-        <v>-3.827162750841379</v>
+        <v>-4.488696958717064</v>
       </c>
       <c r="G65">
-        <v>-10.29443714358509</v>
+        <v>-18.27894991811198</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.994000406809095</v>
       </c>
       <c r="E66">
-        <v>-18.24099425888831</v>
+        <v>-30.47936734662974</v>
       </c>
       <c r="F66">
-        <v>-3.430532154706948</v>
+        <v>-4.640764504685984</v>
       </c>
       <c r="G66">
-        <v>-10.26645641268716</v>
+        <v>-18.39638324475378</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.942687360500924</v>
       </c>
       <c r="E67">
-        <v>-18.97881400048403</v>
+        <v>-31.5027798299932</v>
       </c>
       <c r="F67">
-        <v>-3.531810010108021</v>
+        <v>-4.712621235041826</v>
       </c>
       <c r="G67">
-        <v>-10.67432555476199</v>
+        <v>-17.77468265575189</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.885839181111312</v>
       </c>
       <c r="E68">
-        <v>-17.8728836637528</v>
+        <v>-31.03055508894735</v>
       </c>
       <c r="F68">
-        <v>-3.688414524342073</v>
+        <v>-4.63051345807634</v>
       </c>
       <c r="G68">
-        <v>-10.29145765259974</v>
+        <v>-17.97805939986593</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.825379416908781</v>
       </c>
       <c r="E69">
-        <v>-18.61025508642176</v>
+        <v>-31.15063210573473</v>
       </c>
       <c r="F69">
-        <v>-4.006935872964331</v>
+        <v>-4.603288335015931</v>
       </c>
       <c r="G69">
-        <v>-10.23161623143188</v>
+        <v>-18.3982520477107</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.766922519598651</v>
       </c>
       <c r="E70">
-        <v>-19.01013745519509</v>
+        <v>-31.4344111936624</v>
       </c>
       <c r="F70">
-        <v>-3.453447282170591</v>
+        <v>-4.617555306794347</v>
       </c>
       <c r="G70">
-        <v>-9.961171145237733</v>
+        <v>-17.81159689378753</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.712989990045376</v>
       </c>
       <c r="E71">
-        <v>-18.693049176704</v>
+        <v>-31.14099551304641</v>
       </c>
       <c r="F71">
-        <v>-3.568219242563268</v>
+        <v>-4.693170340056692</v>
       </c>
       <c r="G71">
-        <v>-10.0049961470866</v>
+        <v>-17.871067533855</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.663186301728453</v>
       </c>
       <c r="E72">
-        <v>-18.77689840143002</v>
+        <v>-31.55658262967833</v>
       </c>
       <c r="F72">
-        <v>-3.698585219313645</v>
+        <v>-5.012769394669991</v>
       </c>
       <c r="G72">
-        <v>-10.86150379955239</v>
+        <v>-17.90594082056568</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.621489312202204</v>
       </c>
       <c r="E73">
-        <v>-19.15288854133888</v>
+        <v>-31.3492758823182</v>
       </c>
       <c r="F73">
-        <v>-3.941303495273123</v>
+        <v>-4.887721536645587</v>
       </c>
       <c r="G73">
-        <v>-9.56468034818138</v>
+        <v>-18.084008444032</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.58726124562271</v>
       </c>
       <c r="E74">
-        <v>-19.2807183056274</v>
+        <v>-31.66921257096011</v>
       </c>
       <c r="F74">
-        <v>-3.742798501070666</v>
+        <v>-4.911769870716259</v>
       </c>
       <c r="G74">
-        <v>-9.593935639111919</v>
+        <v>-17.76070553248508</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.558723025801616</v>
       </c>
       <c r="E75">
-        <v>-20.3221631724894</v>
+        <v>-31.38823660844319</v>
       </c>
       <c r="F75">
-        <v>-3.79275899586831</v>
+        <v>-5.117252203552495</v>
       </c>
       <c r="G75">
-        <v>-10.31189365021366</v>
+        <v>-17.67774657181649</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.533307619517306</v>
       </c>
       <c r="E76">
-        <v>-20.75068813936124</v>
+        <v>-31.35617954094289</v>
       </c>
       <c r="F76">
-        <v>-4.283548457944156</v>
+        <v>-5.210007815113568</v>
       </c>
       <c r="G76">
-        <v>-8.97081482607368</v>
+        <v>-17.78508604510905</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.505434925117623</v>
       </c>
       <c r="E77">
-        <v>-20.13428584285918</v>
+        <v>-32.46032792315211</v>
       </c>
       <c r="F77">
-        <v>-4.053441247324898</v>
+        <v>-5.392973465206908</v>
       </c>
       <c r="G77">
-        <v>-8.801003703182303</v>
+        <v>-17.75475482687824</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.473738475439776</v>
       </c>
       <c r="E78">
-        <v>-20.54691586596409</v>
+        <v>-32.15644014639338</v>
       </c>
       <c r="F78">
-        <v>-4.193387293088652</v>
+        <v>-5.079260789357902</v>
       </c>
       <c r="G78">
-        <v>-10.09363269335505</v>
+        <v>-17.45049582854599</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.436576211906408</v>
       </c>
       <c r="E79">
-        <v>-20.65216213037636</v>
+        <v>-32.19265661726972</v>
       </c>
       <c r="F79">
-        <v>-4.189243799339849</v>
+        <v>-5.369128909517324</v>
       </c>
       <c r="G79">
-        <v>-9.515661100381392</v>
+        <v>-17.36935270210568</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.390953344310081</v>
       </c>
       <c r="E80">
-        <v>-20.62036771436851</v>
+        <v>-32.52712970747626</v>
       </c>
       <c r="F80">
-        <v>-4.081582544732803</v>
+        <v>-5.127556265675919</v>
       </c>
       <c r="G80">
-        <v>-9.55155072457263</v>
+        <v>-17.22946228979824</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.338513591866882</v>
       </c>
       <c r="E81">
-        <v>-20.89127008645536</v>
+        <v>-33.17912580967861</v>
       </c>
       <c r="F81">
-        <v>-4.533483470716822</v>
+        <v>-5.277939740714946</v>
       </c>
       <c r="G81">
-        <v>-9.258716418896398</v>
+        <v>-16.75885665448145</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.281376582523995</v>
       </c>
       <c r="E82">
-        <v>-21.64546931853683</v>
+        <v>-33.42831414889869</v>
       </c>
       <c r="F82">
-        <v>-3.913916012201766</v>
+        <v>-5.247654628468597</v>
       </c>
       <c r="G82">
-        <v>-9.793286759850213</v>
+        <v>-17.45665013270349</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.221397235900284</v>
       </c>
       <c r="E83">
-        <v>-22.82777236940742</v>
+        <v>-33.98036456551475</v>
       </c>
       <c r="F83">
-        <v>-4.457464194161912</v>
+        <v>-5.414223574190924</v>
       </c>
       <c r="G83">
-        <v>-9.204294360776318</v>
+        <v>-17.02592829477107</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.16090879512897</v>
       </c>
       <c r="E84">
-        <v>-23.35483693068617</v>
+        <v>-34.51075529095213</v>
       </c>
       <c r="F84">
-        <v>-4.288712500333208</v>
+        <v>-5.439786163873914</v>
       </c>
       <c r="G84">
-        <v>-9.193703925596191</v>
+        <v>-17.11763040620889</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.101755437294337</v>
       </c>
       <c r="E85">
-        <v>-23.51183459605809</v>
+        <v>-35.70169867022936</v>
       </c>
       <c r="F85">
-        <v>-4.439312179264366</v>
+        <v>-5.20532753928775</v>
       </c>
       <c r="G85">
-        <v>-9.26279501100078</v>
+        <v>-17.28059035510674</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.045971653461464</v>
       </c>
       <c r="E86">
-        <v>-25.57537868882133</v>
+        <v>-36.00627477503725</v>
       </c>
       <c r="F86">
-        <v>-4.552351195050387</v>
+        <v>-5.583311585185164</v>
       </c>
       <c r="G86">
-        <v>-8.849638927699736</v>
+        <v>-16.65100735717584</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.998246101624827</v>
       </c>
       <c r="E87">
-        <v>-25.59857353268862</v>
+        <v>-36.26886966155703</v>
       </c>
       <c r="F87">
-        <v>-4.500509477880986</v>
+        <v>-5.708929359982696</v>
       </c>
       <c r="G87">
-        <v>-9.324490337670637</v>
+        <v>-17.26751038968108</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.960648771665242</v>
       </c>
       <c r="E88">
-        <v>-27.44148131485015</v>
+        <v>-36.79628291533437</v>
       </c>
       <c r="F88">
-        <v>-4.541445738192532</v>
+        <v>-5.418101990370832</v>
       </c>
       <c r="G88">
-        <v>-9.329002611240664</v>
+        <v>-16.97296453196104</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.934609111691042</v>
       </c>
       <c r="E89">
-        <v>-27.45182434948367</v>
+        <v>-38.17976568823272</v>
       </c>
       <c r="F89">
-        <v>-4.766904150947278</v>
+        <v>-5.620536759532169</v>
       </c>
       <c r="G89">
-        <v>-9.614504058547412</v>
+        <v>-17.45470022138086</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.923994796374441</v>
       </c>
       <c r="E90">
-        <v>-28.63180882166234</v>
+        <v>-39.00337057719275</v>
       </c>
       <c r="F90">
-        <v>-4.82774110974368</v>
+        <v>-5.41003534860237</v>
       </c>
       <c r="G90">
-        <v>-9.433758203739822</v>
+        <v>-17.5813004486209</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.929404300383641</v>
       </c>
       <c r="E91">
-        <v>-30.407493671417</v>
+        <v>-39.51792749326231</v>
       </c>
       <c r="F91">
-        <v>-4.702699050291094</v>
+        <v>-5.53590743219256</v>
       </c>
       <c r="G91">
-        <v>-9.350428461970827</v>
+        <v>-16.70513146619739</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.95046436736768</v>
       </c>
       <c r="E92">
-        <v>-30.90195548407752</v>
+        <v>-40.36812811006939</v>
       </c>
       <c r="F92">
-        <v>-5.254524279340013</v>
+        <v>-5.693081863199739</v>
       </c>
       <c r="G92">
-        <v>-9.175370124399706</v>
+        <v>-17.67424566990871</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.986103476203815</v>
       </c>
       <c r="E93">
-        <v>-32.30375367009989</v>
+        <v>-41.86642807719522</v>
       </c>
       <c r="F93">
-        <v>-4.78829508238977</v>
+        <v>-5.790017416675337</v>
       </c>
       <c r="G93">
-        <v>-10.79240609305672</v>
+        <v>-17.21623831564162</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.03158642542129</v>
       </c>
       <c r="E94">
-        <v>-33.7073949450434</v>
+        <v>-43.38508353498553</v>
       </c>
       <c r="F94">
-        <v>-4.960156467448583</v>
+        <v>-5.885321086367419</v>
       </c>
       <c r="G94">
-        <v>-10.21090214799266</v>
+        <v>-16.9904988364098</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.088236421605419</v>
       </c>
       <c r="E95">
-        <v>-35.75049524189901</v>
+        <v>-44.33560570072152</v>
       </c>
       <c r="F95">
-        <v>-5.404261627804857</v>
+        <v>-6.049843136237429</v>
       </c>
       <c r="G95">
-        <v>-9.553586710079282</v>
+        <v>-17.07960879069036</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.156223263703273</v>
       </c>
       <c r="E96">
-        <v>-37.15437426172791</v>
+        <v>-46.18765647190454</v>
       </c>
       <c r="F96">
-        <v>-5.273237927336656</v>
+        <v>-6.092669730962164</v>
       </c>
       <c r="G96">
-        <v>-9.974184899752608</v>
+        <v>-16.96445477465235</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.232288176803559</v>
       </c>
       <c r="E97">
-        <v>-39.66184013298907</v>
+        <v>-47.19833035788442</v>
       </c>
       <c r="F97">
-        <v>-5.605346158099632</v>
+        <v>-5.825986786039697</v>
       </c>
       <c r="G97">
-        <v>-10.23323177765504</v>
+        <v>-17.94589082886084</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.321722099296842</v>
       </c>
       <c r="E98">
-        <v>-40.80683082227346</v>
+        <v>-48.81617977457574</v>
       </c>
       <c r="F98">
-        <v>-5.547332275411971</v>
+        <v>-5.914788599987206</v>
       </c>
       <c r="G98">
-        <v>-10.85432653682325</v>
+        <v>-17.35159824637857</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.422949212435832</v>
       </c>
       <c r="E99">
-        <v>-42.32459190644725</v>
+        <v>-50.69855660406963</v>
       </c>
       <c r="F99">
-        <v>-5.460957577954664</v>
+        <v>-5.882157551256128</v>
       </c>
       <c r="G99">
-        <v>-10.77517470352481</v>
+        <v>-18.09580722833396</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.542519540076785</v>
       </c>
       <c r="E100">
-        <v>-44.79253778504348</v>
+        <v>-51.33982361922931</v>
       </c>
       <c r="F100">
-        <v>-5.799538671603114</v>
+        <v>-6.279979339715785</v>
       </c>
       <c r="G100">
-        <v>-11.60626398734007</v>
+        <v>-18.28637547175657</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.673537909907688</v>
       </c>
       <c r="E101">
-        <v>-46.86642717667724</v>
+        <v>-52.71977305028318</v>
       </c>
       <c r="F101">
-        <v>-6.002164793634498</v>
+        <v>-6.498020550745865</v>
       </c>
       <c r="G101">
-        <v>-11.2898056286956</v>
+        <v>-18.28112494653129</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.827897787488046</v>
       </c>
       <c r="E102">
-        <v>-49.65672568479847</v>
+        <v>-55.75633337129702</v>
       </c>
       <c r="F102">
-        <v>-6.247045522698984</v>
+        <v>-6.355195928257383</v>
       </c>
       <c r="G102">
-        <v>-11.94042052243748</v>
+        <v>-18.30942680034651</v>
       </c>
     </row>
   </sheetData>
